--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_antofagasta.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_antofagasta.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:45</t>
+    <t xml:space="preserve">2026-09-09 20:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_antofagasta.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_antofagasta.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:51</t>
+    <t xml:space="preserve">2026-09-18 10:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_antofagasta.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_antofagasta.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:41</t>
+    <t xml:space="preserve">2026-09-23 16:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_antofagasta.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_antofagasta.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 16:25</t>
+    <t xml:space="preserve">2026-10-05 06:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
